--- a/ConfigExporter/xlsx/lan_room_config.xlsx
+++ b/ConfigExporter/xlsx/lan_room_config.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -608,6 +608,57 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>heartbeatIntervalMilliseconds</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>对局中 TCP 心跳发送间隔（毫秒）</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>heartbeatTimeoutMilliseconds</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>对局中超过该时长未收到对端消息则进入等待重连（毫秒）</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>reconnectProbeIntervalMilliseconds</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>client 等待重连时向 host 发起恢复握手的间隔（毫秒）</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
